--- a/data/cammy/inputs/cammy_oki_HSA_corner_plus11.xlsx
+++ b/data/cammy/inputs/cammy_oki_HSA_corner_plus11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dfa238\pyproj\gambit_tekken8\data\cammy\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB42321-B9A4-468D-9637-80AA03F7F6AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9615C78D-3103-4DE4-B296-15AC5AB020AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="375" yWindow="1125" windowWidth="28065" windowHeight="14355" activeTab="1" xr2:uid="{3646A7B2-A3A2-437C-B2D0-C976E94CCFF6}"/>
+    <workbookView xWindow="435" yWindow="825" windowWidth="28365" windowHeight="14355" activeTab="1" xr2:uid="{3646A7B2-A3A2-437C-B2D0-C976E94CCFF6}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="2" r:id="rId1"/>
